--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU02/HRM/post FET_HRM-2031-0280/Panel 02/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU02/HRM/post FET_HRM-2031-0280/Panel 02/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Back_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,17 +434,17 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Radius</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Line</t>
+          <t>Dimple</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Space</t>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -456,26 +456,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Trace 1</t>
+          <t>Pad 1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.77108</v>
+        <v>16.86017</v>
       </c>
       <c r="D2" t="n">
-        <v>15.69154</v>
+        <v>16.32355</v>
       </c>
       <c r="E2" t="n">
-        <v>16.25362</v>
-      </c>
-      <c r="F2" t="n">
-        <v>21.8414</v>
+        <v>16.55839</v>
       </c>
       <c r="G2" t="n">
-        <v>22.0069</v>
+        <v>0.05118</v>
       </c>
       <c r="H2" t="n">
-        <v>35.00664</v>
+        <v>1.86312</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +482,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.64016</v>
+        <v>16.91276</v>
       </c>
       <c r="D3" t="n">
-        <v>16.25969</v>
+        <v>16.46534</v>
       </c>
       <c r="E3" t="n">
-        <v>16.58349</v>
+        <v>16.78428</v>
       </c>
       <c r="F3" t="n">
-        <v>21.55243</v>
+        <v>42.18899</v>
       </c>
       <c r="G3" t="n">
-        <v>22.04572</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>33.95729</v>
+        <v>1.81575</v>
       </c>
     </row>
     <row r="4">
@@ -509,23 +506,25 @@
           <t>Unit 9</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>16.6614</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
       <c r="D4" t="n">
-        <v>15.98531</v>
+        <v>16.24079</v>
       </c>
       <c r="E4" t="n">
-        <v>16.54728</v>
+        <v>16.69742</v>
       </c>
       <c r="F4" t="n">
-        <v>21.66704</v>
+        <v>42.41388</v>
       </c>
       <c r="G4" t="n">
-        <v>21.45745</v>
+        <v>0.05049</v>
       </c>
       <c r="H4" t="n">
-        <v>33.94306</v>
+        <v>1.83561</v>
       </c>
     </row>
     <row r="5">
@@ -534,23 +533,25 @@
           <t>Unit 4</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>16.70927</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>12,5</t>
+        </is>
       </c>
       <c r="D5" t="n">
-        <v>16.41116</v>
+        <v>16.58017</v>
       </c>
       <c r="E5" t="n">
-        <v>16.12974</v>
+        <v>16.79947</v>
       </c>
       <c r="F5" t="n">
-        <v>21.71371</v>
+        <v>42.33182</v>
       </c>
       <c r="G5" t="n">
-        <v>21.74208</v>
+        <v>0.05135</v>
       </c>
       <c r="H5" t="n">
-        <v>34.11527</v>
+        <v>1.79072</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +561,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.71878</v>
+        <v>16.85864</v>
       </c>
       <c r="D6" t="n">
-        <v>16.14833</v>
+        <v>16.4678</v>
       </c>
       <c r="E6" t="n">
-        <v>16.20984</v>
+        <v>16.81679</v>
       </c>
       <c r="F6" t="n">
-        <v>21.3243</v>
+        <v>42.25863</v>
       </c>
       <c r="G6" t="n">
-        <v>21.26923</v>
-      </c>
-      <c r="H6" t="n">
-        <v>34.565</v>
+        <v>0.05121</v>
+      </c>
+      <c r="H6" t="e">
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +586,24 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.80492</v>
+        <v>16.80084</v>
       </c>
       <c r="D7" t="n">
-        <v>15.68344</v>
-      </c>
-      <c r="E7" t="n">
-        <v>16.50945</v>
+        <v>16.44956</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 16.48 </t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>21.49325</v>
+        <v>42.45832</v>
       </c>
       <c r="G7" t="n">
-        <v>21.83401</v>
+        <v>0.05085</v>
       </c>
       <c r="H7" t="n">
-        <v>33.85876</v>
+        <v>1.81952</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +613,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.79881</v>
+        <v>17.08077</v>
       </c>
       <c r="D8" t="n">
-        <v>15.91357</v>
+        <v>16.2251</v>
       </c>
       <c r="E8" t="n">
-        <v>16.3237</v>
+        <v>16.71741</v>
       </c>
       <c r="F8" t="n">
-        <v>21.88818</v>
+        <v>42.46674</v>
       </c>
       <c r="G8" t="n">
-        <v>22.13748</v>
+        <v>0.05018</v>
       </c>
       <c r="H8" t="n">
-        <v>34.74917</v>
+        <v>1.81347</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +638,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.95996</v>
+        <v>16.77489</v>
       </c>
       <c r="D9" t="n">
-        <v>15.99618</v>
+        <v>16.42587</v>
       </c>
       <c r="E9" t="n">
-        <v>16.39687</v>
+        <v>16.47905</v>
       </c>
       <c r="F9" t="n">
-        <v>21.72773</v>
+        <v>42.39387</v>
       </c>
       <c r="G9" t="n">
-        <v>21.62726</v>
+        <v>0.04998</v>
       </c>
       <c r="H9" t="n">
-        <v>34.45633</v>
+        <v>1.81906</v>
       </c>
     </row>
     <row r="10">
@@ -660,22 +663,156 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.90283</v>
+        <v>17.05298</v>
       </c>
       <c r="D10" t="n">
-        <v>15.5133</v>
+        <v>16.52555</v>
       </c>
       <c r="E10" t="n">
-        <v>16.3629</v>
+        <v>17.04655</v>
       </c>
       <c r="F10" t="n">
-        <v>22.17373</v>
+        <v>42.71603</v>
       </c>
       <c r="G10" t="n">
-        <v>21.99133</v>
+        <v>0.05023</v>
       </c>
       <c r="H10" t="n">
-        <v>34.07546</v>
+        <v>1.8401</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>via 1</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.10049</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.10412</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.13311</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.10067</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.12675</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.12773</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.11253</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.11992</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.13272</v>
       </c>
     </row>
   </sheetData>
